--- a/manual-testing/barbora-webshop-testing/test-cases/Test cases.xlsx
+++ b/manual-testing/barbora-webshop-testing/test-cases/Test cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96c6bdc0c0427c4e/Desktop/Martins/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96c6bdc0c0427c4e/Desktop/qa-portfolio/manual-testing/barbora-webshop-testing/test-cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1595" documentId="8_{2E745F09-F5DA-49F8-923B-BDB05765374C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BD785D7-B3D4-43DA-AD07-B96431B3C0DE}"/>
+  <xr:revisionPtr revIDLastSave="1649" documentId="8_{2E745F09-F5DA-49F8-923B-BDB05765374C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33C43228-CFE5-48F0-9BBE-89E650590A9F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{7320CF2E-7D46-4224-BA1E-30842D3EBF44}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="319">
   <si>
     <t>TEST SCENARIO</t>
   </si>
@@ -178,9 +178,6 @@
     <t>Enter e-mail address</t>
   </si>
   <si>
-    <t>loyalcustomer123312@gmail.com</t>
-  </si>
-  <si>
     <t>E-mail address is added into the input window</t>
   </si>
   <si>
@@ -272,9 +269,6 @@
   </si>
   <si>
     <t>Choose street from the drop-down</t>
-  </si>
-  <si>
-    <t>Latgales iela xxx, LV-xxxx</t>
   </si>
   <si>
     <t>Street name is added to the street input field</t>
@@ -570,9 +564,6 @@
     <t>Enter correct password</t>
   </si>
   <si>
-    <t>JanisBerzins1</t>
-  </si>
-  <si>
     <t>Password is added to the input field</t>
   </si>
   <si>
@@ -582,9 +573,6 @@
     <t>E-mail address is not accepted by the system and error message is displayed</t>
   </si>
   <si>
-    <t>loyal@customer123312@gmail.com</t>
-  </si>
-  <si>
     <t>Verify that the message about the incorrect e-mail format is in Latvian</t>
   </si>
   <si>
@@ -597,9 +585,6 @@
     <t>Enter incorrect password</t>
   </si>
   <si>
-    <t>Janis1234</t>
-  </si>
-  <si>
     <t>Webpage navigates to the authentication page</t>
   </si>
   <si>
@@ -693,9 +678,6 @@
     <t>Enter an e-mail address with a leading space into the e-mail input field</t>
   </si>
   <si>
-    <t xml:space="preserve"> loyal@customer123312@gmail.com</t>
-  </si>
-  <si>
     <t>The e-mail address is added and leading space remains visible in the input field</t>
   </si>
   <si>
@@ -705,18 +687,12 @@
     <t>Enter an e-mail address with a trailing space into the e-mail input field</t>
   </si>
   <si>
-    <t xml:space="preserve">loyal@customer123312@gmail.com </t>
-  </si>
-  <si>
     <t>The e-mail address is added and trailing space remains visible in the input field</t>
   </si>
   <si>
     <t>Enter password in ALL CAPS</t>
   </si>
   <si>
-    <t>JANISBERZINS1</t>
-  </si>
-  <si>
     <t>Validate that systems locks account after multiple failed attempts</t>
   </si>
   <si>
@@ -756,21 +732,6 @@
     <t>Enter a name and surname containing long vowels and diacritical marks used in the Latvian language</t>
   </si>
   <si>
-    <t>Name and surname: 'Janis Berzins'
-Phone number: '25427XXX'
-Password: 'JanisBerzins1'</t>
-  </si>
-  <si>
-    <t>Name and surname: 'Janis Berzins'
-Phone number: '25427XXX'
-Password: 'parole'</t>
-  </si>
-  <si>
-    <t>Name and surname: 'Janis Berzins'
-Phone number: '2567837901'
-Password: 'parole'</t>
-  </si>
-  <si>
     <t>Registration performance</t>
   </si>
   <si>
@@ -816,11 +777,6 @@
     <t xml:space="preserve">All input data is accepted. The loading indicator appears, after longer time user is navigated to the next registration page </t>
   </si>
   <si>
-    <t>Name and surname: 'Janis Berzins'
-Phone number: '25427XXX'
-Password: 'Jr7n9kXXX'</t>
-  </si>
-  <si>
     <t>The loading indicator appears, the website navigates to the homepage, and the user is logged in</t>
   </si>
   <si>
@@ -941,9 +897,6 @@
     <t>TC_C_11</t>
   </si>
   <si>
-    <t>loyalcustomer123321@gmail.co</t>
-  </si>
-  <si>
     <t xml:space="preserve">E-mail address is accepted and OTP is sent to non existing e-mail </t>
   </si>
   <si>
@@ -957,10 +910,6 @@
   </si>
   <si>
     <t>The system does not accept value 15. The quantity automatically changes back to the maximum allowed value or error message is dispalyed</t>
-  </si>
-  <si>
-    <t>E-mail: 'loyalcustomer123312@gmail.com'
-Password: 'JanisBerzins1'</t>
   </si>
   <si>
     <t>Verify that cart loads properly with 20 items</t>
@@ -1162,12 +1111,58 @@
   <si>
     <t>Input field indicates red and error message is displayed</t>
   </si>
+  <si>
+    <t>E-mail: 'registered.test.user@example.com'
+Password: 'ValidTestPassword123!'</t>
+  </si>
+  <si>
+    <t>registered.test.user@example.co</t>
+  </si>
+  <si>
+    <t>registered.test.user@example.com</t>
+  </si>
+  <si>
+    <t>Vidzemes iela xxx, LV-xxxx</t>
+  </si>
+  <si>
+    <t>Name and surname: 'Janis Berzins'
+Phone number: correct phone number
+Password: 'JanisBerzins1'</t>
+  </si>
+  <si>
+    <t>Name and surname: 'Janis Berzins'
+Phone number: '2567837901'
+Password: 'ValidTestPassword123!'</t>
+  </si>
+  <si>
+    <t>Name and surname: 'Janis Berzins'
+Phone number: correct phone number
+Password: 'ValidTestPassword123!'</t>
+  </si>
+  <si>
+    <t>ValidTestPassword123!</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> registered.test.user@example.com</t>
+  </si>
+  <si>
+    <t>registered.test@user@example.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">registered.test.user@example.com </t>
+  </si>
+  <si>
+    <t>InvalidPassword123!</t>
+  </si>
+  <si>
+    <t>INVALIDPASSWORD123!</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1230,6 +1225,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1468,7 +1468,40 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1477,40 +1510,9 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
@@ -1862,17 +1864,17 @@
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.35">
       <c r="B1" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="36" x14ac:dyDescent="0.35">
       <c r="B2" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="126.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -1901,30 +1903,30 @@
       <c r="D8" s="1"/>
     </row>
     <row r="9" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
+      <c r="A9" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="21"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>0</v>
@@ -1942,18 +1944,18 @@
         <v>4</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H12" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="17" t="s">
-        <v>239</v>
+      <c r="A13" s="28" t="s">
+        <v>227</v>
       </c>
       <c r="B13" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="C13" t="s">
         <v>8</v>
@@ -1970,10 +1972,10 @@
       <c r="G13" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="25"/>
+      <c r="H13" s="20"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="18"/>
+      <c r="A14" s="29"/>
       <c r="D14" t="s">
         <v>6</v>
       </c>
@@ -1983,10 +1985,10 @@
       <c r="G14" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="25"/>
+      <c r="H14" s="20"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="18"/>
+      <c r="A15" s="29"/>
       <c r="D15" t="s">
         <v>10</v>
       </c>
@@ -1999,10 +2001,10 @@
       <c r="G15" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="25"/>
+      <c r="H15" s="20"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="18"/>
+      <c r="A16" s="29"/>
       <c r="D16" t="s">
         <v>11</v>
       </c>
@@ -2012,11 +2014,11 @@
       <c r="G16" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="25"/>
+      <c r="H16" s="20"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>0</v>
@@ -2034,18 +2036,18 @@
         <v>4</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H19" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="17" t="s">
-        <v>240</v>
+      <c r="A20" s="28" t="s">
+        <v>228</v>
       </c>
       <c r="B20" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="C20" t="s">
         <v>20</v>
@@ -2062,10 +2064,10 @@
       <c r="G20" t="s">
         <v>12</v>
       </c>
-      <c r="H20" s="25"/>
+      <c r="H20" s="20"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="18"/>
+      <c r="A21" s="29"/>
       <c r="D21" t="s">
         <v>6</v>
       </c>
@@ -2075,10 +2077,10 @@
       <c r="G21" t="s">
         <v>13</v>
       </c>
-      <c r="H21" s="25"/>
+      <c r="H21" s="20"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="18"/>
+      <c r="A22" s="29"/>
       <c r="D22" t="s">
         <v>16</v>
       </c>
@@ -2091,10 +2093,10 @@
       <c r="G22" t="s">
         <v>17</v>
       </c>
-      <c r="H22" s="25"/>
+      <c r="H22" s="20"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="18"/>
+      <c r="A23" s="29"/>
       <c r="D23" t="s">
         <v>18</v>
       </c>
@@ -2104,11 +2106,11 @@
       <c r="G23" t="s">
         <v>19</v>
       </c>
-      <c r="H23" s="25"/>
+      <c r="H23" s="20"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>0</v>
@@ -2126,18 +2128,18 @@
         <v>4</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H26" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H26" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="17" t="s">
-        <v>241</v>
+      <c r="A27" s="28" t="s">
+        <v>229</v>
       </c>
       <c r="B27" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="C27" t="s">
         <v>22</v>
@@ -2154,10 +2156,10 @@
       <c r="G27" t="s">
         <v>12</v>
       </c>
-      <c r="H27" s="25"/>
+      <c r="H27" s="20"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="18"/>
+      <c r="A28" s="29"/>
       <c r="D28" t="s">
         <v>6</v>
       </c>
@@ -2167,10 +2169,10 @@
       <c r="G28" t="s">
         <v>13</v>
       </c>
-      <c r="H28" s="25"/>
+      <c r="H28" s="20"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="18"/>
+      <c r="A29" s="29"/>
       <c r="D29" t="s">
         <v>10</v>
       </c>
@@ -2183,10 +2185,10 @@
       <c r="G29" t="s">
         <v>14</v>
       </c>
-      <c r="H29" s="25"/>
+      <c r="H29" s="20"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="18"/>
+      <c r="A30" s="29"/>
       <c r="D30" t="s">
         <v>11</v>
       </c>
@@ -2196,10 +2198,10 @@
       <c r="G30" t="s">
         <v>21</v>
       </c>
-      <c r="H30" s="25"/>
+      <c r="H30" s="20"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="18"/>
+      <c r="A31" s="29"/>
       <c r="D31" t="s">
         <v>23</v>
       </c>
@@ -2209,11 +2211,11 @@
       <c r="G31" t="s">
         <v>24</v>
       </c>
-      <c r="H31" s="25"/>
+      <c r="H31" s="20"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>0</v>
@@ -2231,18 +2233,18 @@
         <v>4</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H34" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H34" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="17" t="s">
-        <v>243</v>
+      <c r="A35" s="28" t="s">
+        <v>231</v>
       </c>
       <c r="B35" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="C35" t="s">
         <v>26</v>
@@ -2259,10 +2261,10 @@
       <c r="G35" t="s">
         <v>12</v>
       </c>
-      <c r="H35" s="25"/>
+      <c r="H35" s="20"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="18"/>
+      <c r="A36" s="29"/>
       <c r="D36" t="s">
         <v>6</v>
       </c>
@@ -2272,10 +2274,10 @@
       <c r="G36" t="s">
         <v>13</v>
       </c>
-      <c r="H36" s="25"/>
+      <c r="H36" s="20"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="18"/>
+      <c r="A37" s="29"/>
       <c r="D37" t="s">
         <v>16</v>
       </c>
@@ -2288,10 +2290,10 @@
       <c r="G37" t="s">
         <v>17</v>
       </c>
-      <c r="H37" s="25"/>
+      <c r="H37" s="20"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="18"/>
+      <c r="A38" s="29"/>
       <c r="D38" t="s">
         <v>25</v>
       </c>
@@ -2301,10 +2303,10 @@
       <c r="G38" t="s">
         <v>21</v>
       </c>
-      <c r="H38" s="25"/>
+      <c r="H38" s="20"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="18"/>
+      <c r="A39" s="29"/>
       <c r="D39" t="s">
         <v>28</v>
       </c>
@@ -2317,11 +2319,11 @@
       <c r="G39" t="s">
         <v>24</v>
       </c>
-      <c r="H39" s="25"/>
+      <c r="H39" s="20"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>0</v>
@@ -2339,21 +2341,21 @@
         <v>4</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H42" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H42" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="17" t="s">
-        <v>244</v>
+      <c r="A43" s="28" t="s">
+        <v>232</v>
       </c>
       <c r="B43" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="C43" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D43" t="s">
         <v>9</v>
@@ -2367,10 +2369,10 @@
       <c r="G43" t="s">
         <v>12</v>
       </c>
-      <c r="H43" s="25"/>
+      <c r="H43" s="20"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="18"/>
+      <c r="A44" s="29"/>
       <c r="D44" t="s">
         <v>6</v>
       </c>
@@ -2380,10 +2382,10 @@
       <c r="G44" t="s">
         <v>13</v>
       </c>
-      <c r="H44" s="25"/>
+      <c r="H44" s="20"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="18"/>
+      <c r="A45" s="29"/>
       <c r="D45" t="s">
         <v>10</v>
       </c>
@@ -2396,10 +2398,10 @@
       <c r="G45" t="s">
         <v>14</v>
       </c>
-      <c r="H45" s="25"/>
+      <c r="H45" s="20"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="18"/>
+      <c r="A46" s="29"/>
       <c r="D46" t="s">
         <v>11</v>
       </c>
@@ -2409,27 +2411,27 @@
       <c r="G46" t="s">
         <v>15</v>
       </c>
-      <c r="H46" s="25"/>
+      <c r="H46" s="20"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="18"/>
+      <c r="A47" s="29"/>
       <c r="D47" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="F47" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="G47" t="s">
-        <v>183</v>
-      </c>
-      <c r="H47" s="25"/>
+        <v>175</v>
+      </c>
+      <c r="H47" s="20"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>0</v>
@@ -2447,18 +2449,18 @@
         <v>4</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H50" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H50" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="17" t="s">
-        <v>245</v>
+      <c r="A51" s="28" t="s">
+        <v>233</v>
       </c>
       <c r="B51" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="C51" t="s">
         <v>33</v>
@@ -2475,10 +2477,10 @@
       <c r="G51" t="s">
         <v>12</v>
       </c>
-      <c r="H51" s="25"/>
+      <c r="H51" s="20"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="18"/>
+      <c r="A52" s="29"/>
       <c r="D52" t="s">
         <v>6</v>
       </c>
@@ -2488,10 +2490,10 @@
       <c r="G52" t="s">
         <v>13</v>
       </c>
-      <c r="H52" s="25"/>
+      <c r="H52" s="20"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="18"/>
+      <c r="A53" s="29"/>
       <c r="D53" t="s">
         <v>16</v>
       </c>
@@ -2504,23 +2506,23 @@
       <c r="G53" t="s">
         <v>17</v>
       </c>
-      <c r="H53" s="25"/>
+      <c r="H53" s="20"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="18"/>
+      <c r="A54" s="29"/>
       <c r="D54" t="s">
         <v>29</v>
       </c>
       <c r="F54" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="G54" t="s">
         <v>30</v>
       </c>
-      <c r="H54" s="25"/>
+      <c r="H54" s="20"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="18"/>
+      <c r="A55" s="29"/>
       <c r="D55" t="s">
         <v>31</v>
       </c>
@@ -2528,16 +2530,16 @@
         <v>15</v>
       </c>
       <c r="F55" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="G55" t="s">
         <v>32</v>
       </c>
-      <c r="H55" s="25"/>
+      <c r="H55" s="20"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>0</v>
@@ -2555,18 +2557,18 @@
         <v>4</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H58" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H58" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="17" t="s">
-        <v>246</v>
+      <c r="A59" s="28" t="s">
+        <v>234</v>
       </c>
       <c r="B59" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="C59" t="s">
         <v>37</v>
@@ -2583,10 +2585,10 @@
       <c r="G59" t="s">
         <v>12</v>
       </c>
-      <c r="H59" s="25"/>
+      <c r="H59" s="20"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="18"/>
+      <c r="A60" s="29"/>
       <c r="D60" t="s">
         <v>6</v>
       </c>
@@ -2596,10 +2598,10 @@
       <c r="G60" t="s">
         <v>13</v>
       </c>
-      <c r="H60" s="25"/>
+      <c r="H60" s="20"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="18"/>
+      <c r="A61" s="29"/>
       <c r="D61" t="s">
         <v>16</v>
       </c>
@@ -2612,10 +2614,10 @@
       <c r="G61" t="s">
         <v>17</v>
       </c>
-      <c r="H61" s="25"/>
+      <c r="H61" s="20"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="18"/>
+      <c r="A62" s="29"/>
       <c r="D62" t="s">
         <v>34</v>
       </c>
@@ -2628,11 +2630,11 @@
       <c r="G62" t="s">
         <v>36</v>
       </c>
-      <c r="H62" s="25"/>
+      <c r="H62" s="20"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>0</v>
@@ -2650,18 +2652,18 @@
         <v>4</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H65" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H65" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="17" t="s">
-        <v>247</v>
+      <c r="A66" s="28" t="s">
+        <v>235</v>
       </c>
       <c r="B66" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="C66" t="s">
         <v>38</v>
@@ -2678,10 +2680,10 @@
       <c r="G66" t="s">
         <v>12</v>
       </c>
-      <c r="H66" s="25"/>
+      <c r="H66" s="20"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="18"/>
+      <c r="A67" s="29"/>
       <c r="D67" t="s">
         <v>6</v>
       </c>
@@ -2691,10 +2693,10 @@
       <c r="G67" t="s">
         <v>13</v>
       </c>
-      <c r="H67" s="25"/>
+      <c r="H67" s="20"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="18"/>
+      <c r="A68" s="29"/>
       <c r="D68" t="s">
         <v>16</v>
       </c>
@@ -2707,10 +2709,10 @@
       <c r="G68" t="s">
         <v>17</v>
       </c>
-      <c r="H68" s="25"/>
+      <c r="H68" s="20"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="18"/>
+      <c r="A69" s="29"/>
       <c r="D69" t="s">
         <v>39</v>
       </c>
@@ -2718,16 +2720,16 @@
         <v>40</v>
       </c>
       <c r="F69" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G69" t="s">
         <v>36</v>
       </c>
-      <c r="H69" s="25"/>
+      <c r="H69" s="20"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>0</v>
@@ -2745,18 +2747,18 @@
         <v>4</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H72" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H72" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="17" t="s">
-        <v>248</v>
+      <c r="A73" s="28" t="s">
+        <v>236</v>
       </c>
       <c r="B73" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="C73" t="s">
         <v>41</v>
@@ -2773,10 +2775,10 @@
       <c r="G73" t="s">
         <v>12</v>
       </c>
-      <c r="H73" s="25"/>
+      <c r="H73" s="20"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="18"/>
+      <c r="A74" s="29"/>
       <c r="D74" t="s">
         <v>6</v>
       </c>
@@ -2786,10 +2788,10 @@
       <c r="G74" t="s">
         <v>13</v>
       </c>
-      <c r="H74" s="25"/>
+      <c r="H74" s="20"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="18"/>
+      <c r="A75" s="29"/>
       <c r="D75" t="s">
         <v>16</v>
       </c>
@@ -2802,10 +2804,10 @@
       <c r="G75" t="s">
         <v>17</v>
       </c>
-      <c r="H75" s="25"/>
+      <c r="H75" s="20"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="18"/>
+      <c r="A76" s="29"/>
       <c r="D76" t="s">
         <v>25</v>
       </c>
@@ -2815,12 +2817,12 @@
       <c r="G76" t="s">
         <v>21</v>
       </c>
-      <c r="H76" s="25"/>
+      <c r="H76" s="20"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="18"/>
+      <c r="A77" s="29"/>
       <c r="D77" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F77" t="s">
         <v>42</v>
@@ -2828,53 +2830,53 @@
       <c r="G77" t="s">
         <v>42</v>
       </c>
-      <c r="H77" s="25"/>
+      <c r="H77" s="20"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="18"/>
+      <c r="A78" s="29"/>
       <c r="D78" t="s">
+        <v>95</v>
+      </c>
+      <c r="F78" t="s">
+        <v>96</v>
+      </c>
+      <c r="G78" t="s">
+        <v>96</v>
+      </c>
+      <c r="H78" s="20"/>
+    </row>
+    <row r="79" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A79" s="29"/>
+      <c r="D79" t="s">
         <v>97</v>
       </c>
-      <c r="F78" t="s">
+      <c r="E79" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="F79" t="s">
         <v>98</v>
       </c>
-      <c r="G78" t="s">
+      <c r="G79" t="s">
         <v>98</v>
       </c>
-      <c r="H78" s="25"/>
-    </row>
-    <row r="79" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A79" s="18"/>
-      <c r="D79" t="s">
+      <c r="H79" s="20"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="29"/>
+      <c r="D80" t="s">
+        <v>114</v>
+      </c>
+      <c r="F80" t="s">
         <v>99</v>
       </c>
-      <c r="E79" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F79" t="s">
-        <v>100</v>
-      </c>
-      <c r="G79" t="s">
-        <v>100</v>
-      </c>
-      <c r="H79" s="25"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="18"/>
-      <c r="D80" t="s">
-        <v>116</v>
-      </c>
-      <c r="F80" t="s">
-        <v>101</v>
-      </c>
       <c r="G80" t="s">
-        <v>101</v>
-      </c>
-      <c r="H80" s="25"/>
+        <v>99</v>
+      </c>
+      <c r="H80" s="20"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>0</v>
@@ -2892,21 +2894,21 @@
         <v>4</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H83" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H83" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="17" t="s">
-        <v>242</v>
+      <c r="A84" s="28" t="s">
+        <v>230</v>
       </c>
       <c r="B84" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="C84" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D84" t="s">
         <v>9</v>
@@ -2920,10 +2922,10 @@
       <c r="G84" t="s">
         <v>12</v>
       </c>
-      <c r="H84" s="25"/>
+      <c r="H84" s="20"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="18"/>
+      <c r="A85" s="29"/>
       <c r="D85" t="s">
         <v>6</v>
       </c>
@@ -2933,10 +2935,10 @@
       <c r="G85" t="s">
         <v>13</v>
       </c>
-      <c r="H85" s="25"/>
+      <c r="H85" s="20"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="18"/>
+      <c r="A86" s="29"/>
       <c r="D86" t="s">
         <v>16</v>
       </c>
@@ -2949,10 +2951,10 @@
       <c r="G86" t="s">
         <v>17</v>
       </c>
-      <c r="H86" s="25"/>
+      <c r="H86" s="20"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="18"/>
+      <c r="A87" s="29"/>
       <c r="D87" t="s">
         <v>25</v>
       </c>
@@ -2962,63 +2964,63 @@
       <c r="G87" t="s">
         <v>21</v>
       </c>
-      <c r="H87" s="25"/>
+      <c r="H87" s="20"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="18"/>
+      <c r="A88" s="29"/>
       <c r="D88" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F88" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G88" t="s">
-        <v>103</v>
-      </c>
-      <c r="H88" s="25"/>
+        <v>101</v>
+      </c>
+      <c r="H88" s="20"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="18"/>
+      <c r="A89" s="29"/>
       <c r="D89" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F89" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G89" t="s">
-        <v>101</v>
-      </c>
-      <c r="H89" s="25"/>
+        <v>99</v>
+      </c>
+      <c r="H89" s="20"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E90" s="6"/>
     </row>
     <row r="94" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="95" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="B95" s="20"/>
-      <c r="C95" s="20"/>
-      <c r="D95" s="20"/>
-      <c r="E95" s="20"/>
-      <c r="F95" s="20"/>
-      <c r="G95" s="20"/>
+      <c r="A95" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B95" s="22"/>
+      <c r="C95" s="22"/>
+      <c r="D95" s="22"/>
+      <c r="E95" s="22"/>
+      <c r="F95" s="22"/>
+      <c r="G95" s="22"/>
       <c r="H95" s="23"/>
     </row>
     <row r="96" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="21"/>
-      <c r="B96" s="22"/>
-      <c r="C96" s="22"/>
-      <c r="D96" s="22"/>
-      <c r="E96" s="22"/>
-      <c r="F96" s="22"/>
-      <c r="G96" s="22"/>
-      <c r="H96" s="24"/>
+      <c r="A96" s="24"/>
+      <c r="B96" s="25"/>
+      <c r="C96" s="25"/>
+      <c r="D96" s="25"/>
+      <c r="E96" s="25"/>
+      <c r="F96" s="25"/>
+      <c r="G96" s="25"/>
+      <c r="H96" s="26"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>0</v>
@@ -3036,75 +3038,75 @@
         <v>4</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H99" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H99" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="17" t="s">
-        <v>249</v>
+      <c r="A100" s="28" t="s">
+        <v>237</v>
       </c>
       <c r="B100" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="C100" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="D100" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="H100" s="25"/>
+        <v>206</v>
+      </c>
+      <c r="H100" s="20"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="18"/>
+      <c r="A101" s="29"/>
       <c r="D101" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="F101" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="G101" t="s">
-        <v>213</v>
-      </c>
-      <c r="H101" s="25"/>
+        <v>201</v>
+      </c>
+      <c r="H101" s="20"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="18"/>
+      <c r="A102" s="29"/>
       <c r="D102" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="F102" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="G102" t="s">
-        <v>217</v>
-      </c>
-      <c r="H102" s="25"/>
+        <v>205</v>
+      </c>
+      <c r="H102" s="20"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="18"/>
+      <c r="A103" s="29"/>
       <c r="D103" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F103" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="G103" t="s">
-        <v>258</v>
-      </c>
-      <c r="H103" s="25"/>
+        <v>244</v>
+      </c>
+      <c r="H103" s="20"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>0</v>
@@ -3122,84 +3124,74 @@
         <v>4</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H107" s="16" t="s">
-        <v>147</v>
+        <v>90</v>
+      </c>
+      <c r="H107" s="19" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="17" t="s">
-        <v>307</v>
+      <c r="A108" s="28" t="s">
+        <v>293</v>
       </c>
       <c r="B108" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="C108" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="D108" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="H108" s="16"/>
+        <v>206</v>
+      </c>
+      <c r="H108" s="19"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" s="18"/>
+      <c r="A109" s="29"/>
       <c r="D109" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="F109" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="G109" t="s">
-        <v>213</v>
-      </c>
-      <c r="H109" s="16"/>
+        <v>201</v>
+      </c>
+      <c r="H109" s="19"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="18"/>
+      <c r="A110" s="29"/>
       <c r="D110" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="F110" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="G110" t="s">
-        <v>217</v>
-      </c>
-      <c r="H110" s="16"/>
+        <v>205</v>
+      </c>
+      <c r="H110" s="19"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="18"/>
+      <c r="A111" s="29"/>
       <c r="D111" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="F111" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="G111" t="s">
-        <v>306</v>
-      </c>
-      <c r="H111" s="16"/>
+        <v>292</v>
+      </c>
+      <c r="H111" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="H12:H16"/>
-    <mergeCell ref="H19:H23"/>
-    <mergeCell ref="H26:H31"/>
-    <mergeCell ref="H34:H39"/>
-    <mergeCell ref="H42:H47"/>
-    <mergeCell ref="H72:H80"/>
-    <mergeCell ref="H83:H89"/>
-    <mergeCell ref="H50:H55"/>
-    <mergeCell ref="H58:H62"/>
-    <mergeCell ref="H65:H69"/>
     <mergeCell ref="H107:H111"/>
     <mergeCell ref="A108:A111"/>
     <mergeCell ref="A9:H10"/>
@@ -3216,6 +3208,16 @@
     <mergeCell ref="A84:A89"/>
     <mergeCell ref="H99:H103"/>
     <mergeCell ref="A100:A103"/>
+    <mergeCell ref="H72:H80"/>
+    <mergeCell ref="H83:H89"/>
+    <mergeCell ref="H50:H55"/>
+    <mergeCell ref="H58:H62"/>
+    <mergeCell ref="H65:H69"/>
+    <mergeCell ref="H12:H16"/>
+    <mergeCell ref="H19:H23"/>
+    <mergeCell ref="H26:H31"/>
+    <mergeCell ref="H34:H39"/>
+    <mergeCell ref="H42:H47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3237,47 +3239,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" x14ac:dyDescent="0.35">
-      <c r="A1" s="30"/>
       <c r="B1" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="36" x14ac:dyDescent="0.35">
+      <c r="B2" s="10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="126.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="11" t="s">
         <v>106</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="36" x14ac:dyDescent="0.35">
-      <c r="A2" s="30"/>
-      <c r="B2" s="10" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="126.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="30"/>
-      <c r="B3" s="11" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="7" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
+      <c r="A7" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="21"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>0</v>
@@ -3295,21 +3294,21 @@
         <v>4</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>147</v>
+        <v>90</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="27" t="s">
-        <v>226</v>
+      <c r="A12" s="17" t="s">
+        <v>214</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
         <v>43</v>
@@ -3320,23 +3319,23 @@
       <c r="G12" t="s">
         <v>44</v>
       </c>
-      <c r="H12" s="16"/>
+      <c r="H12" s="19"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="27"/>
+      <c r="A13" s="17"/>
       <c r="D13" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>250</v>
+        <v>307</v>
       </c>
       <c r="F13" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="G13" t="s">
-        <v>251</v>
-      </c>
-      <c r="H13" s="16"/>
+        <v>238</v>
+      </c>
+      <c r="H13" s="19"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E14" s="5"/>
@@ -3346,7 +3345,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>0</v>
@@ -3364,21 +3363,21 @@
         <v>4</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H16" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="27" t="s">
-        <v>227</v>
+      <c r="A17" s="17" t="s">
+        <v>215</v>
       </c>
       <c r="B17" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="C17" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="D17" t="s">
         <v>43</v>
@@ -3389,30 +3388,30 @@
       <c r="G17" t="s">
         <v>44</v>
       </c>
-      <c r="H17" s="25"/>
+      <c r="H17" s="20"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="27"/>
+      <c r="A18" s="17"/>
       <c r="D18" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>46</v>
+        <v>308</v>
       </c>
       <c r="F18" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="G18" t="s">
-        <v>224</v>
-      </c>
-      <c r="H18" s="25"/>
+        <v>212</v>
+      </c>
+      <c r="H18" s="20"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E19" s="5"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>0</v>
@@ -3430,21 +3429,21 @@
         <v>4</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H21" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="26" t="s">
-        <v>228</v>
+      <c r="A22" s="16" t="s">
+        <v>216</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
         <v>43</v>
@@ -3455,56 +3454,56 @@
       <c r="G22" t="s">
         <v>44</v>
       </c>
-      <c r="H22" s="25"/>
+      <c r="H22" s="20"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="27"/>
+      <c r="A23" s="17"/>
       <c r="D23" t="s">
         <v>45</v>
       </c>
       <c r="E23" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F23" t="s">
         <v>46</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
+        <v>46</v>
+      </c>
+      <c r="H23" s="20"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="17"/>
+      <c r="D24" t="s">
         <v>47</v>
       </c>
-      <c r="G23" t="s">
-        <v>47</v>
-      </c>
-      <c r="H23" s="25"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="27"/>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
         <v>48</v>
       </c>
-      <c r="F24" t="s">
-        <v>49</v>
-      </c>
       <c r="G24" t="s">
-        <v>49</v>
-      </c>
-      <c r="H24" s="25"/>
+        <v>48</v>
+      </c>
+      <c r="H24" s="20"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="27"/>
+      <c r="A25" s="17"/>
       <c r="D25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E25">
         <v>1234</v>
       </c>
       <c r="F25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G25" t="s">
-        <v>61</v>
-      </c>
-      <c r="H25" s="25"/>
+        <v>60</v>
+      </c>
+      <c r="H25" s="20"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>0</v>
@@ -3522,21 +3521,21 @@
         <v>4</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H27" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H27" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="27" t="s">
-        <v>229</v>
+      <c r="A28" s="17" t="s">
+        <v>217</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D28" t="s">
         <v>43</v>
@@ -3547,56 +3546,56 @@
       <c r="G28" t="s">
         <v>44</v>
       </c>
-      <c r="H28" s="25"/>
+      <c r="H28" s="20"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="27"/>
+      <c r="A29" s="17"/>
       <c r="D29" t="s">
         <v>45</v>
       </c>
       <c r="E29" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F29" t="s">
         <v>46</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
+        <v>46</v>
+      </c>
+      <c r="H29" s="20"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="17"/>
+      <c r="D30" t="s">
         <v>47</v>
       </c>
-      <c r="G29" t="s">
-        <v>47</v>
-      </c>
-      <c r="H29" s="25"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="27"/>
-      <c r="D30" t="s">
+      <c r="F30" t="s">
         <v>48</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
+        <v>48</v>
+      </c>
+      <c r="H30" s="20"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="17"/>
+      <c r="D31" t="s">
         <v>49</v>
-      </c>
-      <c r="G30" t="s">
-        <v>49</v>
-      </c>
-      <c r="H30" s="25"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="27"/>
-      <c r="D31" t="s">
-        <v>50</v>
       </c>
       <c r="E31">
         <v>1234</v>
       </c>
       <c r="F31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G31" t="s">
-        <v>51</v>
-      </c>
-      <c r="H31" s="25"/>
+        <v>50</v>
+      </c>
+      <c r="H31" s="20"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>0</v>
@@ -3614,21 +3613,21 @@
         <v>4</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H35" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H35" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="27" t="s">
-        <v>230</v>
+      <c r="A36" s="17" t="s">
+        <v>218</v>
       </c>
       <c r="B36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D36" t="s">
         <v>43</v>
@@ -3639,68 +3638,68 @@
       <c r="G36" t="s">
         <v>44</v>
       </c>
-      <c r="H36" s="25"/>
+      <c r="H36" s="20"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="27"/>
+      <c r="A37" s="17"/>
       <c r="D37" t="s">
         <v>45</v>
       </c>
       <c r="E37" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F37" t="s">
         <v>46</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
+        <v>46</v>
+      </c>
+      <c r="H37" s="20"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="17"/>
+      <c r="D38" t="s">
         <v>47</v>
       </c>
-      <c r="G37" t="s">
-        <v>47</v>
-      </c>
-      <c r="H37" s="25"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="27"/>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
         <v>48</v>
       </c>
-      <c r="F38" t="s">
-        <v>49</v>
-      </c>
       <c r="G38" t="s">
-        <v>49</v>
-      </c>
-      <c r="H38" s="25"/>
+        <v>48</v>
+      </c>
+      <c r="H38" s="20"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="27"/>
+      <c r="A39" s="17"/>
       <c r="D39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E39">
         <v>8020</v>
       </c>
       <c r="F39" t="s">
+        <v>53</v>
+      </c>
+      <c r="G39" t="s">
+        <v>53</v>
+      </c>
+      <c r="H39" s="20"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="17"/>
+      <c r="D40" t="s">
         <v>54</v>
       </c>
-      <c r="G39" t="s">
-        <v>54</v>
-      </c>
-      <c r="H39" s="25"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="27"/>
-      <c r="D40" t="s">
+      <c r="F40" t="s">
         <v>55</v>
       </c>
-      <c r="F40" t="s">
-        <v>56</v>
-      </c>
       <c r="G40" t="s">
-        <v>56</v>
-      </c>
-      <c r="H40" s="25"/>
+        <v>55</v>
+      </c>
+      <c r="H40" s="20"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="27"/>
+      <c r="A41" s="17"/>
       <c r="D41" t="s">
         <v>43</v>
       </c>
@@ -3710,43 +3709,43 @@
       <c r="G41" t="s">
         <v>44</v>
       </c>
-      <c r="H41" s="25"/>
+      <c r="H41" s="20"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="27"/>
+      <c r="A42" s="17"/>
       <c r="D42" t="s">
         <v>45</v>
       </c>
       <c r="E42" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F42" t="s">
         <v>46</v>
       </c>
-      <c r="F42" t="s">
-        <v>47</v>
-      </c>
       <c r="G42" t="s">
-        <v>47</v>
-      </c>
-      <c r="H42" s="25"/>
+        <v>46</v>
+      </c>
+      <c r="H42" s="20"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="27"/>
+      <c r="A43" s="17"/>
       <c r="D43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E43">
         <v>8020</v>
       </c>
       <c r="F43" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="G43" t="s">
-        <v>51</v>
-      </c>
-      <c r="H43" s="25"/>
+        <v>50</v>
+      </c>
+      <c r="H43" s="20"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>0</v>
@@ -3764,21 +3763,21 @@
         <v>4</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H46" s="16" t="s">
-        <v>147</v>
+        <v>90</v>
+      </c>
+      <c r="H46" s="19" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="27" t="s">
-        <v>231</v>
+      <c r="A47" s="17" t="s">
+        <v>219</v>
       </c>
       <c r="B47" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C47" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D47" t="s">
         <v>43</v>
@@ -3789,72 +3788,72 @@
       <c r="G47" t="s">
         <v>44</v>
       </c>
-      <c r="H47" s="16"/>
+      <c r="H47" s="19"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="27"/>
+      <c r="A48" s="17"/>
       <c r="D48" t="s">
         <v>45</v>
       </c>
       <c r="E48" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F48" t="s">
         <v>46</v>
       </c>
-      <c r="F48" t="s">
-        <v>47</v>
-      </c>
       <c r="G48" t="s">
-        <v>47</v>
-      </c>
-      <c r="H48" s="16"/>
+        <v>46</v>
+      </c>
+      <c r="H48" s="19"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="27"/>
+      <c r="A49" s="17"/>
       <c r="D49" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G49" t="s">
-        <v>49</v>
-      </c>
-      <c r="H49" s="16"/>
+        <v>48</v>
+      </c>
+      <c r="H49" s="19"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="27"/>
+      <c r="A50" s="17"/>
       <c r="D50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E50">
         <v>7485</v>
       </c>
       <c r="F50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G50" t="s">
-        <v>61</v>
-      </c>
-      <c r="H50" s="16"/>
+        <v>60</v>
+      </c>
+      <c r="H50" s="19"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="27"/>
+      <c r="A51" s="17"/>
       <c r="D51" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="F51" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="G51" t="s">
-        <v>189</v>
-      </c>
-      <c r="H51" s="16"/>
+        <v>181</v>
+      </c>
+      <c r="H51" s="19"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>0</v>
@@ -3872,21 +3871,21 @@
         <v>4</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H54" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H54" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="27" t="s">
-        <v>232</v>
+      <c r="A55" s="17" t="s">
+        <v>220</v>
       </c>
       <c r="B55" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C55" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="D55" t="s">
         <v>43</v>
@@ -3897,72 +3896,72 @@
       <c r="G55" t="s">
         <v>44</v>
       </c>
-      <c r="H55" s="25"/>
+      <c r="H55" s="20"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="27"/>
+      <c r="A56" s="17"/>
       <c r="D56" t="s">
         <v>45</v>
       </c>
       <c r="E56" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F56" t="s">
         <v>46</v>
       </c>
-      <c r="F56" t="s">
-        <v>47</v>
-      </c>
       <c r="G56" t="s">
-        <v>47</v>
-      </c>
-      <c r="H56" s="25"/>
+        <v>46</v>
+      </c>
+      <c r="H56" s="20"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="27"/>
+      <c r="A57" s="17"/>
       <c r="D57" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F57" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G57" t="s">
-        <v>49</v>
-      </c>
-      <c r="H57" s="25"/>
+        <v>48</v>
+      </c>
+      <c r="H57" s="20"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="27"/>
+      <c r="A58" s="17"/>
       <c r="D58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E58">
         <v>1234</v>
       </c>
       <c r="F58" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G58" t="s">
-        <v>61</v>
-      </c>
-      <c r="H58" s="25"/>
+        <v>60</v>
+      </c>
+      <c r="H58" s="20"/>
     </row>
     <row r="59" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A59" s="27"/>
+      <c r="A59" s="17"/>
       <c r="D59" t="s">
+        <v>58</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="F59" t="s">
+        <v>176</v>
+      </c>
+      <c r="G59" t="s">
         <v>59</v>
       </c>
-      <c r="E59" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="F59" t="s">
-        <v>184</v>
-      </c>
-      <c r="G59" t="s">
-        <v>60</v>
-      </c>
-      <c r="H59" s="25"/>
+      <c r="H59" s="20"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>0</v>
@@ -3980,21 +3979,21 @@
         <v>4</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H62" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H62" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="27" t="s">
-        <v>233</v>
+      <c r="A63" s="17" t="s">
+        <v>221</v>
       </c>
       <c r="B63" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D63" t="s">
         <v>43</v>
@@ -4005,72 +4004,72 @@
       <c r="G63" t="s">
         <v>44</v>
       </c>
-      <c r="H63" s="25"/>
+      <c r="H63" s="20"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="27"/>
+      <c r="A64" s="17"/>
       <c r="D64" t="s">
         <v>45</v>
       </c>
       <c r="E64" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F64" t="s">
         <v>46</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
+        <v>46</v>
+      </c>
+      <c r="H64" s="20"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="17"/>
+      <c r="D65" t="s">
         <v>47</v>
       </c>
-      <c r="G64" t="s">
-        <v>47</v>
-      </c>
-      <c r="H64" s="25"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="27"/>
-      <c r="D65" t="s">
+      <c r="F65" t="s">
         <v>48</v>
       </c>
-      <c r="F65" t="s">
-        <v>49</v>
-      </c>
       <c r="G65" t="s">
-        <v>49</v>
-      </c>
-      <c r="H65" s="25"/>
+        <v>48</v>
+      </c>
+      <c r="H65" s="20"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="27"/>
+      <c r="A66" s="17"/>
       <c r="D66" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E66">
         <v>1234</v>
       </c>
       <c r="F66" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G66" t="s">
-        <v>61</v>
-      </c>
-      <c r="H66" s="25"/>
+        <v>60</v>
+      </c>
+      <c r="H66" s="20"/>
     </row>
     <row r="67" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A67" s="27"/>
+      <c r="A67" s="17"/>
       <c r="D67" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>192</v>
+        <v>312</v>
       </c>
       <c r="F67" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="G67" t="s">
-        <v>186</v>
-      </c>
-      <c r="H67" s="25"/>
+        <v>178</v>
+      </c>
+      <c r="H67" s="20"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>0</v>
@@ -4088,21 +4087,21 @@
         <v>4</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H70" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H70" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="27" t="s">
-        <v>234</v>
+      <c r="A71" s="17" t="s">
+        <v>222</v>
       </c>
       <c r="B71" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D71" t="s">
         <v>43</v>
@@ -4113,159 +4112,159 @@
       <c r="G71" t="s">
         <v>44</v>
       </c>
-      <c r="H71" s="25"/>
+      <c r="H71" s="20"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="27"/>
+      <c r="A72" s="17"/>
       <c r="D72" t="s">
         <v>45</v>
       </c>
       <c r="E72" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F72" t="s">
         <v>46</v>
       </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
+        <v>46</v>
+      </c>
+      <c r="H72" s="20"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="17"/>
+      <c r="D73" t="s">
         <v>47</v>
       </c>
-      <c r="G72" t="s">
-        <v>47</v>
-      </c>
-      <c r="H72" s="25"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="27"/>
-      <c r="D73" t="s">
+      <c r="F73" t="s">
         <v>48</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
+        <v>48</v>
+      </c>
+      <c r="H73" s="20"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="17"/>
+      <c r="D74" t="s">
         <v>49</v>
-      </c>
-      <c r="G73" t="s">
-        <v>49</v>
-      </c>
-      <c r="H73" s="25"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="27"/>
-      <c r="D74" t="s">
-        <v>50</v>
       </c>
       <c r="E74">
         <v>1399</v>
       </c>
       <c r="F74" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G74" t="s">
-        <v>61</v>
-      </c>
-      <c r="H74" s="25"/>
+        <v>60</v>
+      </c>
+      <c r="H74" s="20"/>
     </row>
     <row r="75" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A75" s="27"/>
+      <c r="A75" s="17"/>
       <c r="D75" t="s">
+        <v>71</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="F75" t="s">
         <v>72</v>
       </c>
-      <c r="E75" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
+        <v>72</v>
+      </c>
+      <c r="H75" s="20"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="17"/>
+      <c r="D76" t="s">
+        <v>75</v>
+      </c>
+      <c r="E76" t="s">
         <v>73</v>
       </c>
-      <c r="G75" t="s">
-        <v>73</v>
-      </c>
-      <c r="H75" s="25"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="27"/>
-      <c r="D76" t="s">
+      <c r="F76" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H76" s="20"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="17"/>
+      <c r="D77" t="s">
         <v>76</v>
       </c>
-      <c r="E76" t="s">
-        <v>74</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G76" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="H76" s="25"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="27"/>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
+        <v>309</v>
+      </c>
+      <c r="F77" t="s">
         <v>77</v>
       </c>
-      <c r="E77" t="s">
+      <c r="G77" t="s">
+        <v>77</v>
+      </c>
+      <c r="H77" s="20"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="17"/>
+      <c r="D78" t="s">
         <v>78</v>
-      </c>
-      <c r="F77" t="s">
-        <v>79</v>
-      </c>
-      <c r="G77" t="s">
-        <v>79</v>
-      </c>
-      <c r="H77" s="25"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="27"/>
-      <c r="D78" t="s">
-        <v>80</v>
       </c>
       <c r="E78">
         <v>50</v>
       </c>
       <c r="F78" t="s">
+        <v>79</v>
+      </c>
+      <c r="G78" t="s">
+        <v>79</v>
+      </c>
+      <c r="H78" s="20"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="17"/>
+      <c r="D79" t="s">
+        <v>112</v>
+      </c>
+      <c r="F79" t="s">
         <v>81</v>
       </c>
-      <c r="G78" t="s">
+      <c r="G79" t="s">
         <v>81</v>
       </c>
-      <c r="H78" s="25"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="27"/>
-      <c r="D79" t="s">
-        <v>114</v>
-      </c>
-      <c r="F79" t="s">
+      <c r="H79" s="20"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="17"/>
+      <c r="D80" t="s">
+        <v>82</v>
+      </c>
+      <c r="F80" t="s">
         <v>83</v>
       </c>
-      <c r="G79" t="s">
+      <c r="G80" t="s">
         <v>83</v>
       </c>
-      <c r="H79" s="25"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="27"/>
-      <c r="D80" t="s">
+      <c r="H80" s="20"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="17"/>
+      <c r="D81" t="s">
+        <v>113</v>
+      </c>
+      <c r="F81" t="s">
         <v>84</v>
       </c>
-      <c r="F80" t="s">
-        <v>85</v>
-      </c>
-      <c r="G80" t="s">
-        <v>85</v>
-      </c>
-      <c r="H80" s="25"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="27"/>
-      <c r="D81" t="s">
-        <v>115</v>
-      </c>
-      <c r="F81" t="s">
-        <v>86</v>
-      </c>
       <c r="G81" t="s">
-        <v>86</v>
-      </c>
-      <c r="H81" s="25"/>
+        <v>84</v>
+      </c>
+      <c r="H81" s="20"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>0</v>
@@ -4283,21 +4282,21 @@
         <v>4</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H84" s="16" t="s">
-        <v>147</v>
+        <v>90</v>
+      </c>
+      <c r="H84" s="19" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="27" t="s">
-        <v>235</v>
+      <c r="A85" s="17" t="s">
+        <v>223</v>
       </c>
       <c r="B85" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D85" t="s">
         <v>43</v>
@@ -4308,141 +4307,141 @@
       <c r="G85" t="s">
         <v>44</v>
       </c>
-      <c r="H85" s="16"/>
+      <c r="H85" s="19"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="27"/>
+      <c r="A86" s="17"/>
       <c r="D86" t="s">
         <v>45</v>
       </c>
       <c r="E86" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F86" t="s">
         <v>46</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
+        <v>46</v>
+      </c>
+      <c r="H86" s="19"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="17"/>
+      <c r="D87" t="s">
         <v>47</v>
       </c>
-      <c r="G86" t="s">
-        <v>47</v>
-      </c>
-      <c r="H86" s="16"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="27"/>
-      <c r="D87" t="s">
+      <c r="F87" t="s">
         <v>48</v>
       </c>
-      <c r="F87" t="s">
-        <v>49</v>
-      </c>
       <c r="G87" t="s">
-        <v>49</v>
-      </c>
-      <c r="H87" s="16"/>
+        <v>48</v>
+      </c>
+      <c r="H87" s="19"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="27"/>
+      <c r="A88" s="17"/>
       <c r="D88" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E88">
         <v>8975</v>
       </c>
       <c r="F88" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G88" t="s">
-        <v>61</v>
-      </c>
-      <c r="H88" s="16"/>
+        <v>60</v>
+      </c>
+      <c r="H88" s="19"/>
     </row>
     <row r="89" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A89" s="27"/>
+      <c r="A89" s="17"/>
       <c r="D89" t="s">
+        <v>71</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="F89" t="s">
         <v>72</v>
       </c>
-      <c r="E89" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="F89" t="s">
+      <c r="G89" t="s">
+        <v>72</v>
+      </c>
+      <c r="H89" s="19"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="17"/>
+      <c r="D90" t="s">
+        <v>75</v>
+      </c>
+      <c r="E90" t="s">
         <v>73</v>
       </c>
-      <c r="G89" t="s">
-        <v>73</v>
-      </c>
-      <c r="H89" s="16"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="27"/>
-      <c r="D90" t="s">
+      <c r="F90" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H90" s="19"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="17"/>
+      <c r="D91" t="s">
         <v>76</v>
       </c>
-      <c r="E90" t="s">
-        <v>74</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="H90" s="16"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="27"/>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
+        <v>309</v>
+      </c>
+      <c r="F91" t="s">
         <v>77</v>
       </c>
-      <c r="E91" t="s">
-        <v>78</v>
-      </c>
-      <c r="F91" t="s">
-        <v>79</v>
-      </c>
       <c r="G91" t="s">
-        <v>79</v>
-      </c>
-      <c r="H91" s="16"/>
+        <v>77</v>
+      </c>
+      <c r="H91" s="19"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="27"/>
+      <c r="A92" s="17"/>
       <c r="D92" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E92" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F92" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G92" t="s">
-        <v>94</v>
-      </c>
-      <c r="H92" s="16"/>
+        <v>92</v>
+      </c>
+      <c r="H92" s="19"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="27"/>
+      <c r="A93" s="17"/>
       <c r="D93" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F93" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="G93" t="s">
-        <v>315</v>
-      </c>
-      <c r="H93" s="16"/>
+        <v>301</v>
+      </c>
+      <c r="H93" s="19"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="27"/>
-      <c r="H94" s="16"/>
+      <c r="A94" s="17"/>
+      <c r="H94" s="19"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="27"/>
-      <c r="H95" s="16"/>
+      <c r="A95" s="17"/>
+      <c r="H95" s="19"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>0</v>
@@ -4460,21 +4459,21 @@
         <v>4</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H98" s="16" t="s">
-        <v>147</v>
+        <v>90</v>
+      </c>
+      <c r="H98" s="19" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="26" t="s">
-        <v>236</v>
+      <c r="A99" s="16" t="s">
+        <v>224</v>
       </c>
       <c r="B99" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C99" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D99" t="s">
         <v>43</v>
@@ -4485,164 +4484,164 @@
       <c r="G99" t="s">
         <v>44</v>
       </c>
-      <c r="H99" s="16"/>
+      <c r="H99" s="19"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="27"/>
+      <c r="A100" s="17"/>
       <c r="D100" t="s">
         <v>45</v>
       </c>
       <c r="E100" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F100" t="s">
         <v>46</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
+        <v>46</v>
+      </c>
+      <c r="H100" s="19"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="17"/>
+      <c r="D101" t="s">
         <v>47</v>
       </c>
-      <c r="G100" t="s">
-        <v>47</v>
-      </c>
-      <c r="H100" s="16"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="27"/>
-      <c r="D101" t="s">
+      <c r="F101" t="s">
         <v>48</v>
       </c>
-      <c r="F101" t="s">
-        <v>49</v>
-      </c>
       <c r="G101" t="s">
-        <v>49</v>
-      </c>
-      <c r="H101" s="16"/>
+        <v>48</v>
+      </c>
+      <c r="H101" s="19"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="27"/>
+      <c r="A102" s="17"/>
       <c r="D102" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E102">
         <v>8975</v>
       </c>
       <c r="F102" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G102" t="s">
-        <v>61</v>
-      </c>
-      <c r="H102" s="16"/>
+        <v>60</v>
+      </c>
+      <c r="H102" s="19"/>
     </row>
     <row r="103" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A103" s="27"/>
+      <c r="A103" s="17"/>
       <c r="D103" t="s">
+        <v>71</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="F103" t="s">
         <v>72</v>
       </c>
-      <c r="E103" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="F103" t="s">
+      <c r="G103" t="s">
+        <v>72</v>
+      </c>
+      <c r="H103" s="19"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" s="17"/>
+      <c r="D104" t="s">
+        <v>75</v>
+      </c>
+      <c r="E104" t="s">
         <v>73</v>
       </c>
-      <c r="G103" t="s">
-        <v>73</v>
-      </c>
-      <c r="H103" s="16"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="27"/>
-      <c r="D104" t="s">
+      <c r="F104" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H104" s="19"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="17"/>
+      <c r="D105" t="s">
         <v>76</v>
       </c>
-      <c r="E104" t="s">
-        <v>74</v>
-      </c>
-      <c r="F104" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G104" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="H104" s="16"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="27"/>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
+        <v>309</v>
+      </c>
+      <c r="F105" t="s">
         <v>77</v>
       </c>
-      <c r="E105" t="s">
-        <v>78</v>
-      </c>
-      <c r="F105" t="s">
-        <v>79</v>
-      </c>
       <c r="G105" t="s">
-        <v>79</v>
-      </c>
-      <c r="H105" s="16"/>
+        <v>77</v>
+      </c>
+      <c r="H105" s="19"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="27"/>
+      <c r="A106" s="17"/>
       <c r="D106" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E106" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F106" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G106" t="s">
-        <v>119</v>
-      </c>
-      <c r="H106" s="16"/>
+        <v>117</v>
+      </c>
+      <c r="H106" s="19"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="27"/>
+      <c r="A107" s="17"/>
       <c r="D107" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F107" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="G107" t="s">
-        <v>315</v>
-      </c>
-      <c r="H107" s="16"/>
+        <v>301</v>
+      </c>
+      <c r="H107" s="19"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="27"/>
-      <c r="H108" s="16"/>
+      <c r="A108" s="17"/>
+      <c r="H108" s="19"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" s="27"/>
-      <c r="H109" s="16"/>
+      <c r="A109" s="17"/>
+      <c r="H109" s="19"/>
     </row>
     <row r="113" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="114" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="B114" s="20"/>
-      <c r="C114" s="20"/>
-      <c r="D114" s="20"/>
-      <c r="E114" s="20"/>
-      <c r="F114" s="20"/>
-      <c r="G114" s="20"/>
-      <c r="H114" s="20"/>
+      <c r="A114" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B114" s="22"/>
+      <c r="C114" s="22"/>
+      <c r="D114" s="22"/>
+      <c r="E114" s="22"/>
+      <c r="F114" s="22"/>
+      <c r="G114" s="22"/>
+      <c r="H114" s="22"/>
     </row>
     <row r="115" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="21"/>
-      <c r="B115" s="22"/>
-      <c r="C115" s="22"/>
-      <c r="D115" s="22"/>
-      <c r="E115" s="22"/>
-      <c r="F115" s="22"/>
-      <c r="G115" s="22"/>
-      <c r="H115" s="22"/>
+      <c r="A115" s="24"/>
+      <c r="B115" s="25"/>
+      <c r="C115" s="25"/>
+      <c r="D115" s="25"/>
+      <c r="E115" s="25"/>
+      <c r="F115" s="25"/>
+      <c r="G115" s="25"/>
+      <c r="H115" s="25"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>0</v>
@@ -4660,62 +4659,62 @@
         <v>4</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H118" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H118" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" s="26" t="s">
-        <v>237</v>
+      <c r="A119" s="16" t="s">
+        <v>225</v>
       </c>
       <c r="B119" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="C119" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="D119" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="F119" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="G119" t="s">
-        <v>200</v>
-      </c>
-      <c r="H119" s="25"/>
+        <v>189</v>
+      </c>
+      <c r="H119" s="20"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" s="27"/>
+      <c r="A120" s="17"/>
       <c r="D120" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F120" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="G120" t="s">
-        <v>197</v>
-      </c>
-      <c r="H120" s="25"/>
+        <v>186</v>
+      </c>
+      <c r="H120" s="20"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A121" s="27"/>
+      <c r="A121" s="17"/>
       <c r="D121" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="F121" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="G121" t="s">
-        <v>253</v>
-      </c>
-      <c r="H121" s="25"/>
+        <v>240</v>
+      </c>
+      <c r="H121" s="20"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>0</v>
@@ -4733,21 +4732,21 @@
         <v>4</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H124" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H124" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" s="26" t="s">
-        <v>238</v>
+      <c r="A125" s="16" t="s">
+        <v>226</v>
       </c>
       <c r="B125" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="C125" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="D125" t="s">
         <v>43</v>
@@ -4758,196 +4757,184 @@
       <c r="G125" t="s">
         <v>44</v>
       </c>
-      <c r="H125" s="25"/>
+      <c r="H125" s="20"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A126" s="27"/>
+      <c r="A126" s="17"/>
       <c r="D126" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="F126" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="G126" t="s">
-        <v>200</v>
-      </c>
-      <c r="H126" s="25"/>
+        <v>189</v>
+      </c>
+      <c r="H126" s="20"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A127" s="27"/>
+      <c r="A127" s="17"/>
       <c r="D127" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="F127" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="G127" t="s">
-        <v>203</v>
-      </c>
-      <c r="H127" s="25"/>
+        <v>192</v>
+      </c>
+      <c r="H127" s="20"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A128" s="27"/>
+      <c r="A128" s="17"/>
       <c r="D128" t="s">
         <v>45</v>
       </c>
       <c r="E128" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F128" t="s">
         <v>46</v>
       </c>
-      <c r="F128" t="s">
-        <v>47</v>
-      </c>
       <c r="G128" t="s">
-        <v>47</v>
-      </c>
-      <c r="H128" s="25"/>
+        <v>46</v>
+      </c>
+      <c r="H128" s="20"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A129" s="27"/>
+      <c r="A129" s="17"/>
       <c r="D129" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="F129" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="G129" t="s">
-        <v>205</v>
-      </c>
-      <c r="H129" s="25"/>
+        <v>194</v>
+      </c>
+      <c r="H129" s="20"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A130" s="27"/>
+      <c r="A130" s="17"/>
       <c r="D130" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="E130">
         <v>8975</v>
       </c>
       <c r="F130" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="G130" t="s">
-        <v>207</v>
-      </c>
-      <c r="H130" s="25"/>
+        <v>196</v>
+      </c>
+      <c r="H130" s="20"/>
     </row>
     <row r="131" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A131" s="27"/>
+      <c r="A131" s="17"/>
       <c r="D131" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>209</v>
+        <v>312</v>
       </c>
       <c r="F131" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G131" t="s">
-        <v>208</v>
-      </c>
-      <c r="H131" s="25"/>
+        <v>197</v>
+      </c>
+      <c r="H131" s="20"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A132" s="27"/>
+      <c r="A132" s="17"/>
       <c r="D132" t="s">
+        <v>75</v>
+      </c>
+      <c r="E132" t="s">
+        <v>73</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="G132" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H132" s="20"/>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A133" s="17"/>
+      <c r="D133" t="s">
         <v>76</v>
       </c>
-      <c r="E132" t="s">
-        <v>74</v>
-      </c>
-      <c r="F132" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G132" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="H132" s="25"/>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A133" s="27"/>
-      <c r="D133" t="s">
+      <c r="E133" t="s">
+        <v>309</v>
+      </c>
+      <c r="F133" t="s">
         <v>77</v>
       </c>
-      <c r="E133" t="s">
+      <c r="G133" t="s">
+        <v>77</v>
+      </c>
+      <c r="H133" s="20"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A134" s="17"/>
+      <c r="D134" t="s">
         <v>78</v>
-      </c>
-      <c r="F133" t="s">
-        <v>79</v>
-      </c>
-      <c r="G133" t="s">
-        <v>79</v>
-      </c>
-      <c r="H133" s="25"/>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A134" s="27"/>
-      <c r="D134" t="s">
-        <v>80</v>
       </c>
       <c r="E134">
         <v>50</v>
       </c>
       <c r="F134" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G134" t="s">
-        <v>81</v>
-      </c>
-      <c r="H134" s="25"/>
+        <v>79</v>
+      </c>
+      <c r="H134" s="20"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A135" s="27"/>
+      <c r="A135" s="17"/>
       <c r="D135" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F135" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="G135" t="s">
-        <v>211</v>
-      </c>
-      <c r="H135" s="25"/>
+        <v>199</v>
+      </c>
+      <c r="H135" s="20"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A136" s="27"/>
+      <c r="A136" s="17"/>
       <c r="D136" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F136" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G136" t="s">
-        <v>85</v>
-      </c>
-      <c r="H136" s="25"/>
+        <v>83</v>
+      </c>
+      <c r="H136" s="20"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A137" s="27"/>
+      <c r="A137" s="17"/>
       <c r="D137" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F137" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="G137" t="s">
-        <v>210</v>
-      </c>
-      <c r="H137" s="25"/>
+        <v>198</v>
+      </c>
+      <c r="H137" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="H70:H81"/>
-    <mergeCell ref="H62:H67"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="H54:H59"/>
-    <mergeCell ref="H35:H43"/>
-    <mergeCell ref="H27:H31"/>
-    <mergeCell ref="H21:H25"/>
-    <mergeCell ref="A85:A95"/>
-    <mergeCell ref="A99:A109"/>
-    <mergeCell ref="A119:A121"/>
-    <mergeCell ref="H98:H109"/>
-    <mergeCell ref="H84:H95"/>
     <mergeCell ref="A7:G8"/>
     <mergeCell ref="A125:A137"/>
     <mergeCell ref="A114:H115"/>
@@ -4964,6 +4951,18 @@
     <mergeCell ref="H118:H121"/>
     <mergeCell ref="A63:A67"/>
     <mergeCell ref="A71:A81"/>
+    <mergeCell ref="A85:A95"/>
+    <mergeCell ref="A99:A109"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="H98:H109"/>
+    <mergeCell ref="H84:H95"/>
+    <mergeCell ref="H70:H81"/>
+    <mergeCell ref="H62:H67"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="H54:H59"/>
+    <mergeCell ref="H35:H43"/>
+    <mergeCell ref="H27:H31"/>
+    <mergeCell ref="H21:H25"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E29" r:id="rId1" xr:uid="{089F42AC-C088-40B0-991E-8CC3532A755A}"/>
@@ -5000,48 +4999,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="30"/>
       <c r="B1" s="9" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="31.8" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="30"/>
       <c r="B2" s="10" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="144.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="30"/>
       <c r="B3" s="11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
+      <c r="A9" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="29"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>0</v>
@@ -5059,87 +5055,87 @@
         <v>4</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H12" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="26" t="s">
-        <v>260</v>
+      <c r="A13" s="16" t="s">
+        <v>246</v>
       </c>
       <c r="B13" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="C13" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F13" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G13" t="s">
-        <v>139</v>
-      </c>
-      <c r="H13" s="25"/>
+        <v>134</v>
+      </c>
+      <c r="H13" s="20"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="27"/>
+      <c r="A14" s="17"/>
       <c r="D14" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>46</v>
+        <v>308</v>
       </c>
       <c r="F14" t="s">
+        <v>125</v>
+      </c>
+      <c r="G14" t="s">
+        <v>125</v>
+      </c>
+      <c r="H14" s="20"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="17"/>
+      <c r="D15" t="s">
+        <v>126</v>
+      </c>
+      <c r="E15" t="s">
+        <v>313</v>
+      </c>
+      <c r="F15" t="s">
         <v>127</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G15" t="s">
         <v>127</v>
       </c>
-      <c r="H14" s="25"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="27"/>
-      <c r="D15" t="s">
+      <c r="H15" s="20"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="17"/>
+      <c r="D16" t="s">
         <v>128</v>
       </c>
-      <c r="E15" t="s">
-        <v>129</v>
-      </c>
-      <c r="F15" t="s">
-        <v>130</v>
-      </c>
-      <c r="G15" t="s">
-        <v>130</v>
-      </c>
-      <c r="H15" s="25"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="27"/>
-      <c r="D16" t="s">
-        <v>131</v>
-      </c>
       <c r="F16" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G16" t="s">
-        <v>143</v>
-      </c>
-      <c r="H16" s="25"/>
+        <v>138</v>
+      </c>
+      <c r="H16" s="20"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H17" s="25"/>
+      <c r="H17" s="20"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H18" s="25"/>
+      <c r="H18" s="20"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>0</v>
@@ -5157,87 +5153,87 @@
         <v>4</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H19" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="26" t="s">
-        <v>261</v>
+      <c r="A20" s="16" t="s">
+        <v>247</v>
       </c>
       <c r="B20" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="C20" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D20" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F20" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G20" t="s">
         <v>44</v>
       </c>
-      <c r="H20" s="25"/>
+      <c r="H20" s="20"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="27"/>
+      <c r="A21" s="17"/>
       <c r="D21" t="s">
+        <v>123</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F21" t="s">
         <v>125</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
+        <v>70</v>
+      </c>
+      <c r="H21" s="20"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="17"/>
+      <c r="D22" t="s">
+        <v>126</v>
+      </c>
+      <c r="E22" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="F22" t="s">
         <v>127</v>
       </c>
-      <c r="G21" t="s">
-        <v>71</v>
-      </c>
-      <c r="H21" s="25"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="27"/>
-      <c r="D22" t="s">
+      <c r="G22" t="s">
+        <v>127</v>
+      </c>
+      <c r="H22" s="20"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="17"/>
+      <c r="D23" t="s">
         <v>128</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F23" t="s">
         <v>129</v>
       </c>
-      <c r="F22" t="s">
-        <v>130</v>
-      </c>
-      <c r="G22" t="s">
-        <v>130</v>
-      </c>
-      <c r="H22" s="25"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="27"/>
-      <c r="D23" t="s">
+      <c r="G23" t="s">
         <v>131</v>
       </c>
-      <c r="F23" t="s">
-        <v>132</v>
-      </c>
-      <c r="G23" t="s">
-        <v>135</v>
-      </c>
-      <c r="H23" s="25"/>
+      <c r="H23" s="20"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H24" s="25"/>
+      <c r="H24" s="20"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H25" s="25"/>
+      <c r="H25" s="20"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>0</v>
@@ -5255,85 +5251,85 @@
         <v>4</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H26" s="25"/>
+        <v>90</v>
+      </c>
+      <c r="H26" s="20"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="26" t="s">
-        <v>262</v>
+      <c r="A27" s="16" t="s">
+        <v>248</v>
       </c>
       <c r="B27" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="C27" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D27" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F27" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G27" t="s">
         <v>44</v>
       </c>
-      <c r="H27" s="25"/>
+      <c r="H27" s="20"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="27"/>
+      <c r="A28" s="17"/>
       <c r="D28" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>170</v>
+        <v>314</v>
       </c>
       <c r="F28" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G28" t="s">
-        <v>171</v>
-      </c>
-      <c r="H28" s="25"/>
+        <v>165</v>
+      </c>
+      <c r="H28" s="20"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="27"/>
+      <c r="A29" s="17"/>
       <c r="D29" t="s">
+        <v>126</v>
+      </c>
+      <c r="E29" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="F29" t="s">
+        <v>127</v>
+      </c>
+      <c r="G29" t="s">
+        <v>127</v>
+      </c>
+      <c r="H29" s="20"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="17"/>
+      <c r="D30" t="s">
         <v>128</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F30" t="s">
         <v>129</v>
       </c>
-      <c r="F29" t="s">
-        <v>130</v>
-      </c>
-      <c r="G29" t="s">
-        <v>130</v>
-      </c>
-      <c r="H29" s="25"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="27"/>
-      <c r="D30" t="s">
-        <v>131</v>
-      </c>
-      <c r="F30" t="s">
-        <v>132</v>
-      </c>
       <c r="G30" t="s">
-        <v>132</v>
-      </c>
-      <c r="H30" s="25"/>
+        <v>129</v>
+      </c>
+      <c r="H30" s="20"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H31" s="25"/>
+      <c r="H31" s="20"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H32" s="25"/>
+      <c r="H32" s="20"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>0</v>
@@ -5351,85 +5347,85 @@
         <v>4</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H33" s="25"/>
+        <v>90</v>
+      </c>
+      <c r="H33" s="20"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="26" t="s">
-        <v>263</v>
+      <c r="A34" s="16" t="s">
+        <v>249</v>
       </c>
       <c r="B34" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="C34" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D34" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F34" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G34" t="s">
         <v>44</v>
       </c>
-      <c r="H34" s="25"/>
+      <c r="H34" s="20"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="27"/>
+      <c r="A35" s="17"/>
       <c r="D35" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>174</v>
+        <v>316</v>
       </c>
       <c r="F35" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="G35" t="s">
-        <v>175</v>
-      </c>
-      <c r="H35" s="25"/>
+        <v>168</v>
+      </c>
+      <c r="H35" s="20"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="27"/>
+      <c r="A36" s="17"/>
       <c r="D36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E36" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="F36" t="s">
+        <v>127</v>
+      </c>
+      <c r="G36" t="s">
+        <v>127</v>
+      </c>
+      <c r="H36" s="20"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="17"/>
+      <c r="D37" t="s">
         <v>128</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F37" t="s">
         <v>129</v>
       </c>
-      <c r="F36" t="s">
-        <v>130</v>
-      </c>
-      <c r="G36" t="s">
-        <v>130</v>
-      </c>
-      <c r="H36" s="25"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="27"/>
-      <c r="D37" t="s">
-        <v>131</v>
-      </c>
-      <c r="F37" t="s">
-        <v>132</v>
-      </c>
       <c r="G37" t="s">
-        <v>132</v>
-      </c>
-      <c r="H37" s="25"/>
+        <v>129</v>
+      </c>
+      <c r="H37" s="20"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H38" s="25"/>
+      <c r="H38" s="20"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H39" s="25"/>
+      <c r="H39" s="20"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>0</v>
@@ -5447,77 +5443,77 @@
         <v>4</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H40" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H40" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="26" t="s">
-        <v>264</v>
+      <c r="A41" s="16" t="s">
+        <v>250</v>
       </c>
       <c r="B41" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="C41" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D41" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F41" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G41" t="s">
         <v>44</v>
       </c>
-      <c r="H41" s="25"/>
+      <c r="H41" s="20"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="27"/>
+      <c r="A42" s="17"/>
       <c r="D42" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>46</v>
+        <v>308</v>
       </c>
       <c r="F42" t="s">
+        <v>125</v>
+      </c>
+      <c r="G42" t="s">
+        <v>70</v>
+      </c>
+      <c r="H42" s="20"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="17"/>
+      <c r="D43" t="s">
+        <v>133</v>
+      </c>
+      <c r="E43" s="30" t="s">
+        <v>317</v>
+      </c>
+      <c r="F43" t="s">
         <v>127</v>
       </c>
-      <c r="G42" t="s">
-        <v>71</v>
-      </c>
-      <c r="H42" s="25"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="27"/>
-      <c r="D43" t="s">
-        <v>137</v>
-      </c>
-      <c r="E43" t="s">
-        <v>138</v>
-      </c>
-      <c r="F43" t="s">
-        <v>130</v>
-      </c>
       <c r="G43" t="s">
-        <v>130</v>
-      </c>
-      <c r="H43" s="25"/>
+        <v>127</v>
+      </c>
+      <c r="H43" s="20"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="27"/>
+      <c r="A44" s="17"/>
       <c r="D44" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F44" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G44" t="s">
-        <v>140</v>
-      </c>
-      <c r="H44" s="25"/>
+        <v>135</v>
+      </c>
+      <c r="H44" s="20"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="H45" s="12"/>
@@ -5527,7 +5523,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>0</v>
@@ -5545,108 +5541,108 @@
         <v>4</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H47" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H47" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="26" t="s">
-        <v>265</v>
+      <c r="A48" s="16" t="s">
+        <v>251</v>
       </c>
       <c r="B48" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="C48" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="D48" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F48" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G48" t="s">
         <v>44</v>
       </c>
-      <c r="H48" s="25"/>
+      <c r="H48" s="20"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="27"/>
+      <c r="A49" s="17"/>
       <c r="D49" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>46</v>
+        <v>308</v>
       </c>
       <c r="F49" t="s">
+        <v>125</v>
+      </c>
+      <c r="G49" t="s">
+        <v>70</v>
+      </c>
+      <c r="H49" s="20"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="17"/>
+      <c r="D50" t="s">
+        <v>169</v>
+      </c>
+      <c r="E50" t="s">
+        <v>318</v>
+      </c>
+      <c r="F50" t="s">
         <v>127</v>
       </c>
-      <c r="G49" t="s">
-        <v>71</v>
-      </c>
-      <c r="H49" s="25"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="27"/>
-      <c r="D50" t="s">
-        <v>176</v>
-      </c>
-      <c r="E50" t="s">
-        <v>177</v>
-      </c>
-      <c r="F50" t="s">
-        <v>130</v>
-      </c>
       <c r="G50" t="s">
-        <v>130</v>
-      </c>
-      <c r="H50" s="25"/>
+        <v>127</v>
+      </c>
+      <c r="H50" s="20"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="27"/>
+      <c r="A51" s="17"/>
       <c r="D51" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F51" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G51" t="s">
-        <v>140</v>
-      </c>
-      <c r="H51" s="25"/>
+        <v>135</v>
+      </c>
+      <c r="H51" s="20"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H52" s="25"/>
+      <c r="H52" s="20"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H53" s="25"/>
+      <c r="H53" s="20"/>
     </row>
     <row r="56" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="57" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="B57" s="20"/>
-      <c r="C57" s="20"/>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
-      <c r="F57" s="20"/>
+      <c r="A57" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B57" s="22"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
       <c r="G57" s="23"/>
     </row>
     <row r="58" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="21"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="24"/>
+      <c r="A58" s="24"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="26"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>0</v>
@@ -5664,24 +5660,24 @@
         <v>4</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H61" s="28" t="s">
-        <v>147</v>
+        <v>90</v>
+      </c>
+      <c r="H61" s="27" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="26" t="s">
-        <v>266</v>
+      <c r="A62" s="16" t="s">
+        <v>252</v>
       </c>
       <c r="B62" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C62" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D62" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F62" t="s">
         <v>44</v>
@@ -5689,52 +5685,52 @@
       <c r="G62" t="s">
         <v>44</v>
       </c>
-      <c r="H62" s="28"/>
+      <c r="H62" s="27"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="27"/>
+      <c r="A63" s="17"/>
       <c r="D63" t="s">
+        <v>123</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F63" t="s">
         <v>125</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
+        <v>125</v>
+      </c>
+      <c r="H63" s="27"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="17"/>
+      <c r="D64" t="s">
+        <v>126</v>
+      </c>
+      <c r="E64" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="F64" t="s">
         <v>127</v>
       </c>
-      <c r="G63" t="s">
+      <c r="G64" t="s">
         <v>127</v>
       </c>
-      <c r="H63" s="28"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="27"/>
-      <c r="D64" t="s">
+      <c r="H64" s="27"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="17"/>
+      <c r="D65" t="s">
         <v>128</v>
       </c>
-      <c r="E64" t="s">
-        <v>129</v>
-      </c>
-      <c r="F64" t="s">
-        <v>130</v>
-      </c>
-      <c r="G64" t="s">
-        <v>130</v>
-      </c>
-      <c r="H64" s="28"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="27"/>
-      <c r="D65" t="s">
+      <c r="F65" t="s">
+        <v>297</v>
+      </c>
+      <c r="G65" t="s">
         <v>131</v>
       </c>
-      <c r="F65" t="s">
-        <v>311</v>
-      </c>
-      <c r="G65" t="s">
-        <v>135</v>
-      </c>
-      <c r="H65" s="28"/>
+      <c r="H65" s="27"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="H66" s="14"/>
@@ -5750,7 +5746,7 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>0</v>
@@ -5768,107 +5764,107 @@
         <v>4</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H70" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H70" s="19" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="B71" t="s">
+        <v>278</v>
+      </c>
+      <c r="C71" t="s">
+        <v>298</v>
+      </c>
+      <c r="D71" t="s">
+        <v>122</v>
+      </c>
+      <c r="F71" t="s">
+        <v>134</v>
+      </c>
+      <c r="G71" t="s">
+        <v>134</v>
+      </c>
+      <c r="H71" s="19"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="17"/>
+      <c r="D72" t="s">
+        <v>137</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F72" t="s">
+        <v>125</v>
+      </c>
+      <c r="G72" t="s">
+        <v>125</v>
+      </c>
+      <c r="H72" s="19"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="17"/>
+      <c r="D73" t="s">
+        <v>126</v>
+      </c>
+      <c r="E73" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="F73" t="s">
+        <v>127</v>
+      </c>
+      <c r="G73" t="s">
+        <v>127</v>
+      </c>
+      <c r="H73" s="19"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="17"/>
+      <c r="D74" t="s">
+        <v>144</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H74" s="19"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="17"/>
+      <c r="D75" t="s">
+        <v>128</v>
+      </c>
+      <c r="F75" t="s">
+        <v>146</v>
+      </c>
+      <c r="G75" t="s">
+        <v>138</v>
+      </c>
+      <c r="H75" s="19"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="17"/>
+      <c r="D76" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="26" t="s">
-        <v>267</v>
-      </c>
-      <c r="B71" t="s">
-        <v>292</v>
-      </c>
-      <c r="C71" t="s">
-        <v>312</v>
-      </c>
-      <c r="D71" t="s">
-        <v>124</v>
-      </c>
-      <c r="F71" t="s">
-        <v>139</v>
-      </c>
-      <c r="G71" t="s">
-        <v>139</v>
-      </c>
-      <c r="H71" s="16"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="27"/>
-      <c r="D72" t="s">
-        <v>142</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F72" t="s">
-        <v>127</v>
-      </c>
-      <c r="G72" t="s">
-        <v>127</v>
-      </c>
-      <c r="H72" s="16"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="27"/>
-      <c r="D73" t="s">
-        <v>128</v>
-      </c>
-      <c r="E73" t="s">
-        <v>129</v>
-      </c>
-      <c r="F73" t="s">
-        <v>130</v>
-      </c>
-      <c r="G73" t="s">
-        <v>130</v>
-      </c>
-      <c r="H73" s="16"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="27"/>
-      <c r="D74" t="s">
+      <c r="F76" t="s">
+        <v>148</v>
+      </c>
+      <c r="G76" t="s">
         <v>149</v>
       </c>
-      <c r="F74" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="G74" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="H74" s="16"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="27"/>
-      <c r="D75" t="s">
-        <v>131</v>
-      </c>
-      <c r="F75" t="s">
-        <v>151</v>
-      </c>
-      <c r="G75" t="s">
-        <v>143</v>
-      </c>
-      <c r="H75" s="16"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="27"/>
-      <c r="D76" t="s">
-        <v>152</v>
-      </c>
-      <c r="F76" t="s">
-        <v>153</v>
-      </c>
-      <c r="G76" t="s">
-        <v>154</v>
-      </c>
-      <c r="H76" s="16"/>
+      <c r="H76" s="19"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>0</v>
@@ -5886,133 +5882,133 @@
         <v>4</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H79" s="25" t="s">
-        <v>148</v>
+        <v>90</v>
+      </c>
+      <c r="H79" s="20" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="26" t="s">
-        <v>268</v>
+      <c r="A80" s="16" t="s">
+        <v>254</v>
       </c>
       <c r="B80" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="C80" t="s">
+        <v>152</v>
+      </c>
+      <c r="D80" t="s">
+        <v>122</v>
+      </c>
+      <c r="F80" t="s">
+        <v>134</v>
+      </c>
+      <c r="G80" t="s">
+        <v>134</v>
+      </c>
+      <c r="H80" s="20"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="17"/>
+      <c r="D81" t="s">
+        <v>137</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F81" t="s">
+        <v>125</v>
+      </c>
+      <c r="G81" t="s">
+        <v>125</v>
+      </c>
+      <c r="H81" s="20"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="17"/>
+      <c r="D82" t="s">
+        <v>126</v>
+      </c>
+      <c r="E82" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="F82" t="s">
+        <v>127</v>
+      </c>
+      <c r="G82" t="s">
+        <v>127</v>
+      </c>
+      <c r="H82" s="20"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="17"/>
+      <c r="D83" t="s">
+        <v>144</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H83" s="20"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="17"/>
+      <c r="D84" t="s">
+        <v>153</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="G84" t="s">
+        <v>154</v>
+      </c>
+      <c r="H84" s="20"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="17"/>
+      <c r="D85" t="s">
+        <v>155</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H85" s="20"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="17"/>
+      <c r="D86" t="s">
+        <v>128</v>
+      </c>
+      <c r="F86" t="s">
+        <v>146</v>
+      </c>
+      <c r="G86" t="s">
+        <v>138</v>
+      </c>
+      <c r="H86" s="20"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="17"/>
+      <c r="D87" t="s">
         <v>157</v>
       </c>
-      <c r="D80" t="s">
-        <v>124</v>
-      </c>
-      <c r="F80" t="s">
-        <v>139</v>
-      </c>
-      <c r="G80" t="s">
-        <v>139</v>
-      </c>
-      <c r="H80" s="25"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="27"/>
-      <c r="D81" t="s">
-        <v>142</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F81" t="s">
-        <v>127</v>
-      </c>
-      <c r="G81" t="s">
-        <v>127</v>
-      </c>
-      <c r="H81" s="25"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="27"/>
-      <c r="D82" t="s">
-        <v>128</v>
-      </c>
-      <c r="E82" t="s">
-        <v>129</v>
-      </c>
-      <c r="F82" t="s">
-        <v>130</v>
-      </c>
-      <c r="G82" t="s">
-        <v>130</v>
-      </c>
-      <c r="H82" s="25"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="27"/>
-      <c r="D83" t="s">
-        <v>149</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="G83" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="H83" s="25"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="27"/>
-      <c r="D84" t="s">
+      <c r="F87" t="s">
         <v>158</v>
       </c>
-      <c r="F84" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G84" t="s">
-        <v>159</v>
-      </c>
-      <c r="H84" s="25"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="27"/>
-      <c r="D85" t="s">
-        <v>160</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="H85" s="25"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="27"/>
-      <c r="D86" t="s">
-        <v>131</v>
-      </c>
-      <c r="F86" t="s">
-        <v>151</v>
-      </c>
-      <c r="G86" t="s">
-        <v>143</v>
-      </c>
-      <c r="H86" s="25"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="27"/>
-      <c r="D87" t="s">
-        <v>162</v>
-      </c>
-      <c r="F87" t="s">
-        <v>163</v>
-      </c>
       <c r="G87" t="s">
-        <v>163</v>
-      </c>
-      <c r="H87" s="25"/>
+        <v>158</v>
+      </c>
+      <c r="H87" s="20"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>0</v>
@@ -6030,81 +6026,81 @@
         <v>4</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H90" s="16" t="s">
-        <v>147</v>
+        <v>90</v>
+      </c>
+      <c r="H90" s="19" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="26" t="s">
-        <v>269</v>
+      <c r="A91" s="16" t="s">
+        <v>255</v>
       </c>
       <c r="B91" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="C91" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D91" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F91" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G91" t="s">
-        <v>139</v>
-      </c>
-      <c r="H91" s="16"/>
+        <v>134</v>
+      </c>
+      <c r="H91" s="19"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="27"/>
+      <c r="A92" s="17"/>
       <c r="D92" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>46</v>
+        <v>308</v>
       </c>
       <c r="F92" t="s">
+        <v>125</v>
+      </c>
+      <c r="G92" t="s">
+        <v>70</v>
+      </c>
+      <c r="H92" s="19"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="17"/>
+      <c r="D93" t="s">
+        <v>133</v>
+      </c>
+      <c r="E93" s="30" t="s">
+        <v>317</v>
+      </c>
+      <c r="F93" t="s">
         <v>127</v>
       </c>
-      <c r="G92" t="s">
-        <v>71</v>
-      </c>
-      <c r="H92" s="16"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="27"/>
-      <c r="D93" t="s">
-        <v>137</v>
-      </c>
-      <c r="E93" t="s">
-        <v>138</v>
-      </c>
-      <c r="F93" t="s">
-        <v>130</v>
-      </c>
       <c r="G93" t="s">
-        <v>130</v>
-      </c>
-      <c r="H93" s="16"/>
+        <v>127</v>
+      </c>
+      <c r="H93" s="19"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="27"/>
+      <c r="A94" s="17"/>
       <c r="D94" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="F94" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="G94" t="s">
-        <v>180</v>
-      </c>
-      <c r="H94" s="16"/>
+        <v>172</v>
+      </c>
+      <c r="H94" s="19"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>0</v>
@@ -6122,60 +6118,60 @@
         <v>4</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H98" s="16" t="s">
-        <v>147</v>
+        <v>90</v>
+      </c>
+      <c r="H98" s="19" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="26" t="s">
-        <v>270</v>
+      <c r="A99" s="16" t="s">
+        <v>256</v>
       </c>
       <c r="B99" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="C99" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D99" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F99" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G99" t="s">
-        <v>139</v>
-      </c>
-      <c r="H99" s="16"/>
+        <v>134</v>
+      </c>
+      <c r="H99" s="19"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="27"/>
+      <c r="A100" s="17"/>
       <c r="D100" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E100" s="5"/>
       <c r="F100" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G100" t="s">
-        <v>167</v>
-      </c>
-      <c r="H100" s="16"/>
+        <v>162</v>
+      </c>
+      <c r="H100" s="19"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E101" s="5"/>
-      <c r="H101" s="16"/>
+      <c r="H101" s="19"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H102" s="16"/>
+      <c r="H102" s="19"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="H103" s="15"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>0</v>
@@ -6193,24 +6189,24 @@
         <v>4</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="H104" s="28" t="s">
-        <v>147</v>
+        <v>90</v>
+      </c>
+      <c r="H104" s="27" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="26" t="s">
-        <v>271</v>
+      <c r="A105" s="16" t="s">
+        <v>257</v>
       </c>
       <c r="B105" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C105" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="D105" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F105" t="s">
         <v>44</v>
@@ -6218,55 +6214,63 @@
       <c r="G105" t="s">
         <v>44</v>
       </c>
-      <c r="H105" s="28"/>
+      <c r="H105" s="27"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="27"/>
+      <c r="A106" s="17"/>
       <c r="D106" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>133</v>
+        <v>308</v>
       </c>
       <c r="F106" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G106" t="s">
-        <v>290</v>
-      </c>
-      <c r="H106" s="28"/>
+        <v>276</v>
+      </c>
+      <c r="H106" s="27"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="27"/>
+      <c r="A107" s="17"/>
       <c r="D107" t="s">
+        <v>126</v>
+      </c>
+      <c r="E107" s="30" t="s">
+        <v>313</v>
+      </c>
+      <c r="F107" t="s">
+        <v>127</v>
+      </c>
+      <c r="G107" t="s">
+        <v>127</v>
+      </c>
+      <c r="H107" s="27"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" s="17"/>
+      <c r="D108" t="s">
         <v>128</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F108" t="s">
         <v>129</v>
       </c>
-      <c r="F107" t="s">
-        <v>130</v>
-      </c>
-      <c r="G107" t="s">
-        <v>130</v>
-      </c>
-      <c r="H107" s="28"/>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="27"/>
-      <c r="D108" t="s">
+      <c r="G108" t="s">
         <v>131</v>
       </c>
-      <c r="F108" t="s">
-        <v>132</v>
-      </c>
-      <c r="G108" t="s">
-        <v>135</v>
-      </c>
-      <c r="H108" s="28"/>
+      <c r="H108" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A57:G58"/>
+    <mergeCell ref="H104:H108"/>
+    <mergeCell ref="H61:H65"/>
+    <mergeCell ref="H79:H87"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="A105:A108"/>
+    <mergeCell ref="A71:A76"/>
+    <mergeCell ref="A80:A87"/>
     <mergeCell ref="A48:A51"/>
     <mergeCell ref="A99:A100"/>
     <mergeCell ref="A9:H10"/>
@@ -6283,14 +6287,6 @@
     <mergeCell ref="H98:H102"/>
     <mergeCell ref="H90:H94"/>
     <mergeCell ref="H47:H53"/>
-    <mergeCell ref="A57:G58"/>
-    <mergeCell ref="H104:H108"/>
-    <mergeCell ref="H61:H65"/>
-    <mergeCell ref="H79:H87"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="A105:A108"/>
-    <mergeCell ref="A71:A76"/>
-    <mergeCell ref="A80:A87"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E14" r:id="rId1" xr:uid="{38E63D1D-0650-4201-910D-AF248A73598B}"/>
@@ -6298,6 +6294,12 @@
     <hyperlink ref="E81" r:id="rId3" xr:uid="{E3A1DC75-84A7-4145-9077-407DE6A29F9D}"/>
     <hyperlink ref="E35" r:id="rId4" xr:uid="{8443D795-03C0-443D-8DBA-331EE65E4FFC}"/>
     <hyperlink ref="E106" r:id="rId5" xr:uid="{66C7106C-B869-4DE2-A3F3-BCD030C4BFCE}"/>
+    <hyperlink ref="E21" r:id="rId6" xr:uid="{34FE2CA0-8BD1-4CA8-B8D8-108DA692746D}"/>
+    <hyperlink ref="E28" r:id="rId7" display="registered.test.user@example.com" xr:uid="{20B55E40-C199-4580-B989-D8518A5CFEAD}"/>
+    <hyperlink ref="E42" r:id="rId8" xr:uid="{901DC4A2-94AB-4383-AB7E-E120CD96807D}"/>
+    <hyperlink ref="E49" r:id="rId9" xr:uid="{5330FA99-DD20-40B5-92FA-423640DC1A7A}"/>
+    <hyperlink ref="E63" r:id="rId10" xr:uid="{39CC3CA5-945D-4763-8FF6-3FA473DAE5A3}"/>
+    <hyperlink ref="E92" r:id="rId11" xr:uid="{0A8B123C-22C6-495F-A3CD-761E723AD112}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/manual-testing/barbora-webshop-testing/test-cases/Test cases.xlsx
+++ b/manual-testing/barbora-webshop-testing/test-cases/Test cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96c6bdc0c0427c4e/Desktop/qa-portfolio/manual-testing/barbora-webshop-testing/test-cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1649" documentId="8_{2E745F09-F5DA-49F8-923B-BDB05765374C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33C43228-CFE5-48F0-9BBE-89E650590A9F}"/>
+  <xr:revisionPtr revIDLastSave="1655" documentId="8_{2E745F09-F5DA-49F8-923B-BDB05765374C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E81466A-5A3F-4775-BFD4-A6C99444572E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{7320CF2E-7D46-4224-BA1E-30842D3EBF44}"/>
+    <workbookView minimized="1" xWindow="1920" yWindow="864" windowWidth="16668" windowHeight="11376" activeTab="2" xr2:uid="{7320CF2E-7D46-4224-BA1E-30842D3EBF44}"/>
   </bookViews>
   <sheets>
     <sheet name="Cart TC" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="318">
   <si>
     <t>TEST SCENARIO</t>
   </si>
@@ -1123,11 +1123,6 @@
   </si>
   <si>
     <t>Vidzemes iela xxx, LV-xxxx</t>
-  </si>
-  <si>
-    <t>Name and surname: 'Janis Berzins'
-Phone number: correct phone number
-Password: 'JanisBerzins1'</t>
   </si>
   <si>
     <t>Name and surname: 'Janis Berzins'
@@ -3949,7 +3944,7 @@
         <v>58</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F59" t="s">
         <v>176</v>
@@ -4057,7 +4052,7 @@
         <v>177</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F67" t="s">
         <v>178</v>
@@ -4165,7 +4160,7 @@
         <v>71</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F75" t="s">
         <v>72</v>
@@ -4360,7 +4355,7 @@
         <v>71</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F89" t="s">
         <v>72</v>
@@ -4537,7 +4532,7 @@
         <v>71</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F103" t="s">
         <v>72</v>
@@ -4836,7 +4831,7 @@
         <v>71</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F131" t="s">
         <v>197</v>
@@ -5104,7 +5099,7 @@
         <v>126</v>
       </c>
       <c r="E15" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F15" t="s">
         <v>127</v>
@@ -5186,7 +5181,7 @@
         <v>123</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F21" t="s">
         <v>125</v>
@@ -5202,7 +5197,7 @@
         <v>126</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F22" t="s">
         <v>127</v>
@@ -5282,7 +5277,7 @@
         <v>164</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F28" t="s">
         <v>165</v>
@@ -5298,7 +5293,7 @@
         <v>126</v>
       </c>
       <c r="E29" s="30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F29" t="s">
         <v>127</v>
@@ -5378,7 +5373,7 @@
         <v>167</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F35" t="s">
         <v>168</v>
@@ -5394,7 +5389,7 @@
         <v>126</v>
       </c>
       <c r="E36" s="30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F36" t="s">
         <v>127</v>
@@ -5492,7 +5487,7 @@
         <v>133</v>
       </c>
       <c r="E43" s="30" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F43" t="s">
         <v>127</v>
@@ -5590,7 +5585,7 @@
         <v>169</v>
       </c>
       <c r="E50" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F50" t="s">
         <v>127</v>
@@ -5693,7 +5688,7 @@
         <v>123</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F63" t="s">
         <v>125</v>
@@ -5709,7 +5704,7 @@
         <v>126</v>
       </c>
       <c r="E64" s="30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F64" t="s">
         <v>127</v>
@@ -5813,7 +5808,7 @@
         <v>126</v>
       </c>
       <c r="E73" s="30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F73" t="s">
         <v>127</v>
@@ -5931,7 +5926,7 @@
         <v>126</v>
       </c>
       <c r="E82" s="30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F82" t="s">
         <v>127</v>
@@ -6075,7 +6070,7 @@
         <v>133</v>
       </c>
       <c r="E93" s="30" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F93" t="s">
         <v>127</v>
@@ -6238,7 +6233,7 @@
         <v>126</v>
       </c>
       <c r="E107" s="30" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F107" t="s">
         <v>127</v>

--- a/manual-testing/barbora-webshop-testing/test-cases/Test cases.xlsx
+++ b/manual-testing/barbora-webshop-testing/test-cases/Test cases.xlsx
@@ -2,15 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96c6bdc0c0427c4e/Desktop/qa-portfolio/manual-testing/barbora-webshop-testing/test-cases/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1655" documentId="8_{2E745F09-F5DA-49F8-923B-BDB05765374C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E81466A-5A3F-4775-BFD4-A6C99444572E}"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="1656" documentId="8_{2E745F09-F5DA-49F8-923B-BDB05765374C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70B9483E-45FA-4AC1-A065-6A4262D582C2}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1920" yWindow="864" windowWidth="16668" windowHeight="11376" activeTab="2" xr2:uid="{7320CF2E-7D46-4224-BA1E-30842D3EBF44}"/>
+    <workbookView xWindow="3180" yWindow="648" windowWidth="16668" windowHeight="11376" activeTab="2" xr2:uid="{7320CF2E-7D46-4224-BA1E-30842D3EBF44}"/>
   </bookViews>
   <sheets>
     <sheet name="Cart TC" sheetId="1" r:id="rId1"/>
@@ -3215,6 +3210,7 @@
     <mergeCell ref="H42:H47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4975,6 +4971,7 @@
     <hyperlink ref="E18" r:id="rId13" xr:uid="{6AF9C6E4-08EE-4408-BEF2-8B1209B56F0D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId14"/>
 </worksheet>
 </file>
 
@@ -6297,5 +6294,6 @@
     <hyperlink ref="E92" r:id="rId11" xr:uid="{0A8B123C-22C6-495F-A3CD-761E723AD112}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId12"/>
 </worksheet>
 </file>